--- a/public/volunteer-roster/templates/working-bee-roster.xlsx
+++ b/public/volunteer-roster/templates/working-bee-roster.xlsx
@@ -118,7 +118,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shift</t>
+          <t xml:space="preserve">Area</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
